--- a/selenium-tests/reports/excel/Test_Summary.xlsx
+++ b/selenium-tests/reports/excel/Test_Summary.xlsx
@@ -49,7 +49,7 @@
     <t>Total Suite Execution Time</t>
   </si>
   <si>
-    <t>6/8/2026, 5:08:50 pm</t>
+    <t>6/8/2026, 5:16:58 pm</t>
   </si>
   <si>
     <t>Performance</t>
